--- a/counselor_forms/017_dream_job_survey--counselor_forms.xlsx
+++ b/counselor_forms/017_dream_job_survey--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dream Job Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to answer these questions about your dream job.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,17 +542,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>job_preferences</t>
+          <t>motivators</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What would you do</t>
+          <t>What motivates you</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,22 +570,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>career_values</t>
+          <t>work_environment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Career values</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>What matters most in your career</t>
-        </is>
-      </c>
+          <t>Work environment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -593,64 +593,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>work_environment</t>
+          <t>career_values</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Work environment</t>
+          <t>Career values</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>career_stage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Job satisfaction</t>
+          <t>Current career stage</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>career_stage</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Current career stage</t>
+          <t>Job satisfaction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ideal_job</t>
+          <t>ideal_job_description</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,7 +673,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -685,18 +685,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>job_preferences_2</t>
+          <t>job_preferences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What would you do</t>
+          <t>Ideal job preferences</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,18 +708,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>career_values_2</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Career values</t>
+          <t>Job satisfaction 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,41 +731,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>work_environment_2</t>
+          <t>career_stage_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Work environment</t>
+          <t>Ideal career stage</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>job_satisfaction_2</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Job satisfaction</t>
+          <t>Job type</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,41 +777,156 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>career_stage_2</t>
+          <t>job_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Current career stage</t>
+          <t>Job location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ideal_job_description</t>
+          <t>job_industry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ideal job description</t>
+          <t>Job industry</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Job satisfaction 3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dream_job_title</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dream job title</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ideal_company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ideal company</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ideal_workplace</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ideal workplace</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ideal_culture</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ideal company culture</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -826,12 +941,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,51 +969,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>job_preferences_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>accounting</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>job_preferences_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>job_preferences_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -956,51 +1071,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>career_stage_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>career_starter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Career starter</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>career_stage_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>mid-career</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Mid-career</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>career_stage_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>late_career</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Late career</t>
         </is>
       </c>
     </row>
@@ -1046,318 +1161,522 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_at_all_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>career_stage_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>career_starter</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Career starter</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>career_stage_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mid-career</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mid-career</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>career_stage_choices</t>
+          <t>job_preferences_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>late_career</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Late career</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_preferences_2_choices</t>
+          <t>job_preferences_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_preferences_2_choices</t>
+          <t>job_preferences_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_preferences_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>accounting</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Accounting</t>
+          <t>Highly satisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>career_values_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>personal_growth</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Personal growth</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>career_values_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>job_security</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Job security</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>career_values_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>financial_gain</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financial gain</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_environment_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_environment_2_choices</t>
+          <t>career_stage_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>career_starter</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Career starter</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>work_environment_2_choices</t>
+          <t>career_stage_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>mid-career</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Mid-career</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>career_stage_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>highly_satisfied</t>
+          <t>late_career</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Highly satisfied</t>
+          <t>Late career</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>creative</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Somewhat satisfied</t>
+          <t>Creative</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>not_at_all_satisfied</t>
+          <t>analytical</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Not at all satisfied</t>
+          <t>Analytical</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>career_stage_2_choices</t>
+          <t>job_type_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>career_starter</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Career starter</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>career_stage_2_choices</t>
+          <t>job_location_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mid-career</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mid-career</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>career_stage_2_choices</t>
+          <t>job_location_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>late_career</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Late career</t>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>job_location_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>job_industry_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>job_industry_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>healthcare</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>job_industry_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>highly_satisfied</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Highly satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Somewhat satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Somewhat dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>job_satisfaction_3_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>not_at_all_satisfied</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Not at all satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ideal_culture_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>collaborative</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Collaborative</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ideal_culture_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>competitive</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ideal_culture_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Flexible</t>
         </is>
       </c>
     </row>
